--- a/model/Outputs/11. Interest rate/10/Summary.xlsx
+++ b/model/Outputs/11. Interest rate/10/Summary.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.11" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,28 +537,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0625</v>
+        <v>0.0703125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09326171875</v>
+        <v>0.1048507690429688</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1237831115722656</v>
+        <v>0.139085479080677</v>
       </c>
       <c r="E3" t="n">
-        <v>0.184349000453949</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>0.1843305711227003</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -564,28 +556,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3276370.810888279</v>
+        <v>3443385.651242558</v>
       </c>
       <c r="C4" t="n">
-        <v>3276370.810888279</v>
+        <v>3443385.651242558</v>
       </c>
       <c r="D4" t="n">
-        <v>3276370.810888279</v>
+        <v>3443385.651242558</v>
       </c>
       <c r="E4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>3443385.651242558</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -594,28 +575,788 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3421155.030438011</v>
+        <v>3504567.770349653</v>
       </c>
       <c r="C5" t="n">
-        <v>3392952.988818015</v>
+        <v>3461828.431168785</v>
       </c>
       <c r="D5" t="n">
-        <v>3417568.182107281</v>
+        <v>3464232.050417361</v>
       </c>
       <c r="E5" t="n">
-        <v>3307021.355165984</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>3451476.772823278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4600000000000001</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4700000000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4900000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feed-in Tariffs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02730560302734375</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0467035248875618</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0853099357773317</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1235393309357562</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1613953921570867</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.251362687653405</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Base NPV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3472483.769443947</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3468788.015709392</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3467899.505167294</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3445741.068091149</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3448528.192956976</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3467716.306152389</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3444835.764029701</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4600000000000001</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4700000000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4900000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feed-in Tariffs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0312042236328125</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.06414832919836044</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.09681897295013187</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Base NPV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3477018.088404682</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3454629.595092581</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3450409.91099717</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3448139.716236944</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4600000000000001</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4700000000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4900000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feed-in Tariffs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Base NPV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3443385.651242558</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3443385.651242558</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3443385.651242558</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
